--- a/question_bank/ENGLISH - Vocabulary.xlsx
+++ b/question_bank/ENGLISH - Vocabulary.xlsx
@@ -9,18 +9,19 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7500"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7500" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Syllabus" sheetId="29" r:id="rId1"/>
     <sheet name="Synonyms" sheetId="3" r:id="rId2"/>
     <sheet name="Antonyms" sheetId="2" r:id="rId3"/>
-    <sheet name="Homophones (1)" sheetId="27" r:id="rId4"/>
-    <sheet name="Homophones (2)" sheetId="28" r:id="rId5"/>
-    <sheet name="One Word Subs" sheetId="17" r:id="rId6"/>
-    <sheet name="One Word Subs (MS)" sheetId="16" r:id="rId7"/>
-    <sheet name="One Word Subs (Guide)" sheetId="21" r:id="rId8"/>
-    <sheet name="Correct Spelling" sheetId="12" r:id="rId9"/>
+    <sheet name="Antonyms (PCDas)" sheetId="31" r:id="rId4"/>
+    <sheet name="Homophones (int1)" sheetId="27" r:id="rId5"/>
+    <sheet name="Homophones (int2)" sheetId="28" r:id="rId6"/>
+    <sheet name="One Word Subs" sheetId="17" r:id="rId7"/>
+    <sheet name="One Word Subs (MS)" sheetId="16" r:id="rId8"/>
+    <sheet name="One Word Subs (Guide)" sheetId="21" r:id="rId9"/>
+    <sheet name="Correct Spelling" sheetId="12" r:id="rId10"/>
   </sheets>
   <calcPr calcId="162913" refMode="R1C1"/>
   <extLst>
@@ -32,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1011" uniqueCount="917">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1341" uniqueCount="1243">
   <si>
     <t>Amazing</t>
   </si>
@@ -3516,12 +3517,990 @@
   <si>
     <t>Write Synonym of following:</t>
   </si>
+  <si>
+    <t>Write the Antonyms of following:</t>
+  </si>
+  <si>
+    <t>Opposite word (বিপরীত শব্দ)</t>
+  </si>
+  <si>
+    <t>moral (নৈতিক)</t>
+  </si>
+  <si>
+    <t>amoral (অনৈতিক)</t>
+  </si>
+  <si>
+    <t>political (রাজনৈতিক)</t>
+  </si>
+  <si>
+    <t>apolitical (অরাজনৈতিক)</t>
+  </si>
+  <si>
+    <t>sexual (যৌন)</t>
+  </si>
+  <si>
+    <t>asexual (অযৌন)</t>
+  </si>
+  <si>
+    <t>theist (আস্তিক)</t>
+  </si>
+  <si>
+    <t>atheist (নাস্তিক)</t>
+  </si>
+  <si>
+    <t>use (ব্যবহার)</t>
+  </si>
+  <si>
+    <t>abuse (অপব্যবহার)</t>
+  </si>
+  <si>
+    <t>normal (স্বাভাবিক)</t>
+  </si>
+  <si>
+    <t>abnormal (অস্বাভাবিক)</t>
+  </si>
+  <si>
+    <t>dote (সংক্রমণ)</t>
+  </si>
+  <si>
+    <t>anti-dote (প্রতিষেধক)</t>
+  </si>
+  <si>
+    <t>climax (চরম সীমায় আরোহণ)</t>
+  </si>
+  <si>
+    <t>anti-climax (নিম্নসীমায় অবরোহণ)</t>
+  </si>
+  <si>
+    <t>sympathy (সহানুভূতি)</t>
+  </si>
+  <si>
+    <t>anti-pathy (বিরূপতা)</t>
+  </si>
+  <si>
+    <t>septic (সংক্রামক পচন সৃষ্টিকারী)</t>
+  </si>
+  <si>
+    <t>anti-septic (পচন নিরোধক)</t>
+  </si>
+  <si>
+    <t>social (সামাজিক)</t>
+  </si>
+  <si>
+    <t>anti-social (সমাজবিরোধী)</t>
+  </si>
+  <si>
+    <t>toxin (বিষক্রিয়া)</t>
+  </si>
+  <si>
+    <t>anti-toxin (বিষক্রিয়া-প্রতিষেধক)</t>
+  </si>
+  <si>
+    <t>control (নিয়ন্ত্রণ করা)</t>
+  </si>
+  <si>
+    <t>decontrol (নিয়ন্ত্রণ তুলে দেওয়া)</t>
+  </si>
+  <si>
+    <t>merit (গুণ)</t>
+  </si>
+  <si>
+    <t>demerit (দোষ)</t>
+  </si>
+  <si>
+    <t>hoard (মজুত করা)</t>
+  </si>
+  <si>
+    <t>dehoard (মজুত উদ্ধার করা)</t>
+  </si>
+  <si>
+    <t>code (সাঙ্কেতিক লিপি)</t>
+  </si>
+  <si>
+    <t>decode (সাঙ্কেতিক লিপি পাঠ করা)</t>
+  </si>
+  <si>
+    <t>entrain (ট্রেনে ওঠা)</t>
+  </si>
+  <si>
+    <t>detrain (ট্রেন থেকে নামা)</t>
+  </si>
+  <si>
+    <t>enthron (সিংহাসনে বসানো)</t>
+  </si>
+  <si>
+    <t>dethrone (সিংহাসন থেকে নামানো)</t>
+  </si>
+  <si>
+    <t>agree (সম্মত হওয়া)</t>
+  </si>
+  <si>
+    <t>disagree (অসম্মত হওয়া)</t>
+  </si>
+  <si>
+    <t>allow (অনুমোদন করা)</t>
+  </si>
+  <si>
+    <t>disallow (নামঞ্জুর করা)</t>
+  </si>
+  <si>
+    <t>comfort (আরাম)</t>
+  </si>
+  <si>
+    <t>discomfort (অস্বাচ্ছন্দ্য)</t>
+  </si>
+  <si>
+    <t>honest (সৎ)</t>
+  </si>
+  <si>
+    <t>dishonest (অসৎ)</t>
+  </si>
+  <si>
+    <t>honesty (সততা)</t>
+  </si>
+  <si>
+    <t>dishonesty (অসততা)</t>
+  </si>
+  <si>
+    <t>honour (সম্মান)</t>
+  </si>
+  <si>
+    <t>dishonour (অসম্মান)</t>
+  </si>
+  <si>
+    <t>like (পছন্দ করা)</t>
+  </si>
+  <si>
+    <t>dislike (অপছন্দ করা)</t>
+  </si>
+  <si>
+    <t>obey (মান্য করা)</t>
+  </si>
+  <si>
+    <t>disobey (অমান্য করা)</t>
+  </si>
+  <si>
+    <t>obedient (বাধ্য করা)</t>
+  </si>
+  <si>
+    <t>disobedient (অবাধ্য)</t>
+  </si>
+  <si>
+    <t>please (খুশি করা)</t>
+  </si>
+  <si>
+    <t>displease (অখুশি করা)</t>
+  </si>
+  <si>
+    <t>appear (অ ရှိত হওয়া)</t>
+  </si>
+  <si>
+    <t>disappear (অ ရှိত হওয়া)</t>
+  </si>
+  <si>
+    <t>legal (আইন অনুযায়ী)</t>
+  </si>
+  <si>
+    <t>illegal (বেআইনি)</t>
+  </si>
+  <si>
+    <t>legible (যা সহজে পড়া যায়)</t>
+  </si>
+  <si>
+    <t>illegible (যা সহজে পড়া যায় না)</t>
+  </si>
+  <si>
+    <t>logical (যুক্তিসঙ্গত)</t>
+  </si>
+  <si>
+    <t>illogical (যুক্তিসঙ্গত)</t>
+  </si>
+  <si>
+    <t>liberal (উদার)</t>
+  </si>
+  <si>
+    <t>Illiberal (অনূদার)</t>
+  </si>
+  <si>
+    <t>literate (সাক্ষর)</t>
+  </si>
+  <si>
+    <t>Illiterate (নিরক্ষর)</t>
+  </si>
+  <si>
+    <t>balance (ভারসাম্য)</t>
+  </si>
+  <si>
+    <t>imbalance (ভারসাম্যহীনতা)</t>
+  </si>
+  <si>
+    <t>partial (পক্ষপাতিপূর্ণ)</t>
+  </si>
+  <si>
+    <t>impartial (নিরপেক্ষ)</t>
+  </si>
+  <si>
+    <t>possible (সম্ভব)</t>
+  </si>
+  <si>
+    <t>impossible (অসম্ভব)</t>
+  </si>
+  <si>
+    <t>patient (ধৈর্যশীল)</t>
+  </si>
+  <si>
+    <t>impatient (অধীর)</t>
+  </si>
+  <si>
+    <t>personal (ব্যক্তিগত)</t>
+  </si>
+  <si>
+    <t>impersonal (নৈর্ব্যক্তিক)</t>
+  </si>
+  <si>
+    <t>potent (বীর্যশীল)</t>
+  </si>
+  <si>
+    <t>impotent (নির্বীর্য)</t>
+  </si>
+  <si>
+    <t>probable (সম্ভব)</t>
+  </si>
+  <si>
+    <t>improbable (অসম্ভব)</t>
+  </si>
+  <si>
+    <t>pure (খাটি, পবিত্র)</t>
+  </si>
+  <si>
+    <t>impure (ভেজাল, দূষিত)</t>
+  </si>
+  <si>
+    <t>immoral (অনৈতিক)</t>
+  </si>
+  <si>
+    <t>mortal (মরণশীল)</t>
+  </si>
+  <si>
+    <t>immortal (অমর)</t>
+  </si>
+  <si>
+    <t>mature (পরিণত)</t>
+  </si>
+  <si>
+    <t>immature (অপরিপক্ক)</t>
+  </si>
+  <si>
+    <t>mobile (চলনশীল)</t>
+  </si>
+  <si>
+    <t>immobile (অচল)</t>
+  </si>
+  <si>
+    <t>movable</t>
+  </si>
+  <si>
+    <t>immovable</t>
+  </si>
+  <si>
+    <t>measurable (পরিমাপযোগ্য)</t>
+  </si>
+  <si>
+    <t>immeasurable (অপরিমের)</t>
+  </si>
+  <si>
+    <t>ability (ক্ষমতা)</t>
+  </si>
+  <si>
+    <t>inability (অক্ষমতা)</t>
+  </si>
+  <si>
+    <t>active (সক্রিয়)</t>
+  </si>
+  <si>
+    <t>inactive (নিষ্ক্রিয়)</t>
+  </si>
+  <si>
+    <t>capable (যোগ্য)</t>
+  </si>
+  <si>
+    <t>incapable (অযোগ্য)</t>
+  </si>
+  <si>
+    <t>animate (প্রাণী)</t>
+  </si>
+  <si>
+    <t>Inanimate (অযোানী, জড়)</t>
+  </si>
+  <si>
+    <t>accurate (সঠিক)</t>
+  </si>
+  <si>
+    <t>inaccurate (সঠিক নয়)</t>
+  </si>
+  <si>
+    <t>credible (বিশ্বাসযোগ্য)</t>
+  </si>
+  <si>
+    <t>incredible (অবিশ্বাস্য)</t>
+  </si>
+  <si>
+    <t>attentive (মনোযোগী)</t>
+  </si>
+  <si>
+    <t>Inattentive (মনোযোগী)</t>
+  </si>
+  <si>
+    <t>decent (শোডন)</t>
+  </si>
+  <si>
+    <t>Indecent (অশোভন)</t>
+  </si>
+  <si>
+    <t>definite (নির্দিষ্ট)</t>
+  </si>
+  <si>
+    <t>Indefinite (অনির্দিষ্ট)</t>
+  </si>
+  <si>
+    <t>distinct (স্পষ্ট)</t>
+  </si>
+  <si>
+    <t>Indistinct (অস্পষ্ট)</t>
+  </si>
+  <si>
+    <t>divisible (ভাজ্য)</t>
+  </si>
+  <si>
+    <t>Indivisible (অবিভাজ্য)</t>
+  </si>
+  <si>
+    <t>discipline (শৃঙ্খলা)</t>
+  </si>
+  <si>
+    <t>Indiscipline (বিশৃঙ্খলা)</t>
+  </si>
+  <si>
+    <t>justice (ন্যায়)</t>
+  </si>
+  <si>
+    <t>injustice (অন্যায়)</t>
+  </si>
+  <si>
+    <t>sensible (বোধশক্তিসম্পন্ন)</t>
+  </si>
+  <si>
+    <t>insensible (বোধশক্তিহীন)</t>
+  </si>
+  <si>
+    <t>separable (পৃথক করার যোগ্য)</t>
+  </si>
+  <si>
+    <t>inseparable (যা পৃথক করা যায় না)</t>
+  </si>
+  <si>
+    <t>stability (স্থিরতা)</t>
+  </si>
+  <si>
+    <t>instability (অস্থিরতা)</t>
+  </si>
+  <si>
+    <t>sufficient (যথেষ্ট)</t>
+  </si>
+  <si>
+    <t>insufficient (অপ্রতুল)</t>
+  </si>
+  <si>
+    <t>valid (আইনসিদ্ধ)</t>
+  </si>
+  <si>
+    <t>invalid (বাতিল)</t>
+  </si>
+  <si>
+    <t>visible (দৃষ্টিগোচর)</t>
+  </si>
+  <si>
+    <t>invisible (অদৃশ্য)</t>
+  </si>
+  <si>
+    <t>rational (যুক্তিসিদ্ধ)</t>
+  </si>
+  <si>
+    <t>irrational (যা যুক্তিসিদ্ধ নয়)</t>
+  </si>
+  <si>
+    <t>regular (নিয়মিত)</t>
+  </si>
+  <si>
+    <t>irregular (অনিয়মিত)</t>
+  </si>
+  <si>
+    <t>relevant (প্রাসঙ্গিক)</t>
+  </si>
+  <si>
+    <t>irrelevant (অপ্রাসঙ্গিক)</t>
+  </si>
+  <si>
+    <t>repairable (সংস্কারযোগ্য)</t>
+  </si>
+  <si>
+    <t>irrepairable (সংস্কারের অযোগ্য)</t>
+  </si>
+  <si>
+    <t>recoverable (আরোগ্যের যোগ্য)</t>
+  </si>
+  <si>
+    <t>irrecoverable (দুরারোগ্য)</t>
+  </si>
+  <si>
+    <t>resistible (প্রতিরোধ্য)</t>
+  </si>
+  <si>
+    <t>irresistible (অপ্রতিরোধ্য)</t>
+  </si>
+  <si>
+    <t>responsible (দায়ী)</t>
+  </si>
+  <si>
+    <t>irresponsible (দায়িত্বহীন)</t>
+  </si>
+  <si>
+    <t>resolute (দৃঢ়প্রতিজ্ঞ)</t>
+  </si>
+  <si>
+    <t>irresolute (অস্থিরচিত্ত)</t>
+  </si>
+  <si>
+    <t>practice (অভ্যাস)</t>
+  </si>
+  <si>
+    <t>malpractice (অসৎ অভ্যাস)</t>
+  </si>
+  <si>
+    <t>nutrition (পুষ্টি)</t>
+  </si>
+  <si>
+    <t>malnutrition (অপুষ্টি)</t>
+  </si>
+  <si>
+    <t>conduct (ব্যবহার)</t>
+  </si>
+  <si>
+    <t>misconduct (খারাপ ব্যবহার, দুর্ব্যবহার)</t>
+  </si>
+  <si>
+    <t>fortune (সৌভাগ্য)</t>
+  </si>
+  <si>
+    <t>misfortune (দুর্ভাগ্য)</t>
+  </si>
+  <si>
+    <t>interpret (ব্যাখ্যা করা)</t>
+  </si>
+  <si>
+    <t>misinterpret (ভুল ব্যাখ্যা করা)</t>
+  </si>
+  <si>
+    <t>lead (চালনা করা)</t>
+  </si>
+  <si>
+    <t>mislead (ভুলপথে চালনা করা)</t>
+  </si>
+  <si>
+    <t>happening (ঘটনা)</t>
+  </si>
+  <si>
+    <t>mishap (দুর্ঘটনা)</t>
+  </si>
+  <si>
+    <t>misuse (অপব্যবহার)</t>
+  </si>
+  <si>
+    <t>understand (বোঝা)</t>
+  </si>
+  <si>
+    <t>misunderstand (ভুল বোঝা)</t>
+  </si>
+  <si>
+    <t>sense (অর্থযুক্ত বিষয়)</t>
+  </si>
+  <si>
+    <t>nonsense (অর্থহীন কথা)</t>
+  </si>
+  <si>
+    <t>stop (বিরাম)</t>
+  </si>
+  <si>
+    <t>nonstop (অবিরাম)</t>
+  </si>
+  <si>
+    <t>violence (হিংসা)</t>
+  </si>
+  <si>
+    <t>non-violence (অহিংসা)</t>
+  </si>
+  <si>
+    <t>able (সক্ষম)</t>
+  </si>
+  <si>
+    <t>unable (অক্ষম)</t>
+  </si>
+  <si>
+    <t>armed (সশস্ত্র)</t>
+  </si>
+  <si>
+    <t>unarmed (নিরস্ত্র)</t>
+  </si>
+  <si>
+    <t>kind (দয়ালু)</t>
+  </si>
+  <si>
+    <t>unkind (নির্দয়)</t>
+  </si>
+  <si>
+    <t>common (সাধারণ)</t>
+  </si>
+  <si>
+    <t>uncommon (অসাধারণ)</t>
+  </si>
+  <si>
+    <t>fit (উপযুক্ত)</t>
+  </si>
+  <si>
+    <t>unfit (অনুপযুক্ত)</t>
+  </si>
+  <si>
+    <t>fortunate (সৌভাগ্যবান)</t>
+  </si>
+  <si>
+    <t>unfortunate (হতভাগ্য)</t>
+  </si>
+  <si>
+    <t>[কিন্তু fortune (সৌভাগ্য)।</t>
+  </si>
+  <si>
+    <t>[misfortune, unfortune নয়)</t>
+  </si>
+  <si>
+    <t>conscious (সচেতন)</t>
+  </si>
+  <si>
+    <t>unconscious (অচেতন)</t>
+  </si>
+  <si>
+    <t>developed (উন্নত)</t>
+  </si>
+  <si>
+    <t>undeveloped (অনুন্নত)</t>
+  </si>
+  <si>
+    <t>controlled (নিয়ন্ত্রিত)</t>
+  </si>
+  <si>
+    <t>uncontrolled (অনিয়ন্ত্রিত)</t>
+  </si>
+  <si>
+    <t>pleasant (আনন্দদায়ক)</t>
+  </si>
+  <si>
+    <t>unpleasant (অপ্রীতিকর)</t>
+  </si>
+  <si>
+    <t>popular (জনপ্রিয়)</t>
+  </si>
+  <si>
+    <t>unpopular (জনগণের কাছে অপ্রিয়)</t>
+  </si>
+  <si>
+    <t>wise (জ্ঞানী, অভিজ্ঞ)</t>
+  </si>
+  <si>
+    <t>unwise (অনভিজ্ঞ)</t>
+  </si>
+  <si>
+    <t>unsocial (অসামাজিক)</t>
+  </si>
+  <si>
+    <t>careful (যত্নবান)</t>
+  </si>
+  <si>
+    <t>careless (যত্নহীন)</t>
+  </si>
+  <si>
+    <t>colourful (রঙিন)</t>
+  </si>
+  <si>
+    <t>colourless (রঙহীন)</t>
+  </si>
+  <si>
+    <t>hopeful (আশাপূর্ণ)</t>
+  </si>
+  <si>
+    <t>hopeless (আশাহীন)</t>
+  </si>
+  <si>
+    <t>fearful (ভীতিদায়ক)</t>
+  </si>
+  <si>
+    <t>fearless (ভীতিহীন)</t>
+  </si>
+  <si>
+    <t>cheerful (আনন্দদায়ক)</t>
+  </si>
+  <si>
+    <t>cheerless (আনন্দহীন)</t>
+  </si>
+  <si>
+    <t>faithful (বিশ্বস্ত)</t>
+  </si>
+  <si>
+    <t>faithless (বিশ্বাসহীন)</t>
+  </si>
+  <si>
+    <t>merciful (দয়ালু)</t>
+  </si>
+  <si>
+    <t>merciless (নির্দয়)</t>
+  </si>
+  <si>
+    <t>useful (প্রয়োজনীয়)</t>
+  </si>
+  <si>
+    <t>useless (নিষ্প্রয়োজনীয়)</t>
+  </si>
+  <si>
+    <t>accept (গ্রহণ করা)</t>
+  </si>
+  <si>
+    <t>reject (বর্জন করা)</t>
+  </si>
+  <si>
+    <t>big (বড়)</t>
+  </si>
+  <si>
+    <t>small (ছোট)</t>
+  </si>
+  <si>
+    <t>bold (সাহসী)</t>
+  </si>
+  <si>
+    <t>timid, coward (ভীরু)</t>
+  </si>
+  <si>
+    <t>cold (ঠাণ্ডা)</t>
+  </si>
+  <si>
+    <t>hot (গরম)</t>
+  </si>
+  <si>
+    <t>cool (ঠাণ্ডা)</t>
+  </si>
+  <si>
+    <t>warm (উষ্ণ)</t>
+  </si>
+  <si>
+    <t>different (আলাদা)</t>
+  </si>
+  <si>
+    <t>similar (অনুরূপ)</t>
+  </si>
+  <si>
+    <t>drowsy (তন্দ্রালু)</t>
+  </si>
+  <si>
+    <t>wakeful (জাগ্রত)</t>
+  </si>
+  <si>
+    <t>dead (মৃত)</t>
+  </si>
+  <si>
+    <t>alive (জীবিত)</t>
+  </si>
+  <si>
+    <t>early (সকাল সকাল)</t>
+  </si>
+  <si>
+    <t>late (দেরী)</t>
+  </si>
+  <si>
+    <t>entirely (সামগ্রিকভাবে)</t>
+  </si>
+  <si>
+    <t>partially (আংশিকভাবে)</t>
+  </si>
+  <si>
+    <t>exposed (প্রকাশিত)</t>
+  </si>
+  <si>
+    <t>concealed (গুপ্ত)</t>
+  </si>
+  <si>
+    <t>expanding (প্রসারমান)</t>
+  </si>
+  <si>
+    <t>contracting (সংকোচনশীল)</t>
+  </si>
+  <si>
+    <t>fat (মোটা)</t>
+  </si>
+  <si>
+    <t>thin (পাতলা)</t>
+  </si>
+  <si>
+    <t>forget (ভুলে যাওয়া)</t>
+  </si>
+  <si>
+    <t>remember (স্মরণ করা)</t>
+  </si>
+  <si>
+    <t>general (সাধারণ)</t>
+  </si>
+  <si>
+    <t>specific (নির্দিষ্ট)</t>
+  </si>
+  <si>
+    <t>growing (বর্ধিষ্ণু)</t>
+  </si>
+  <si>
+    <t>decaying (ক্ষয়িষ্ণু)</t>
+  </si>
+  <si>
+    <t>hard (কঠিন)</t>
+  </si>
+  <si>
+    <t>soft (কোমল) / easy (সহজ)</t>
+  </si>
+  <si>
+    <t>hope (আশা)</t>
+  </si>
+  <si>
+    <t>despair (হতাশা)</t>
+  </si>
+  <si>
+    <t>humble (বিনয়ী)</t>
+  </si>
+  <si>
+    <t>proud (অহংকারী)</t>
+  </si>
+  <si>
+    <t>long (লম্বা)</t>
+  </si>
+  <si>
+    <t>short (ছোট)</t>
+  </si>
+  <si>
+    <t>lend (ধার দেওয়া)</t>
+  </si>
+  <si>
+    <t>borrow (ধার করা)</t>
+  </si>
+  <si>
+    <t>life (জীবন)</t>
+  </si>
+  <si>
+    <t>death (মৃত্যু)</t>
+  </si>
+  <si>
+    <t>liberty (স্বাধীনতা)</t>
+  </si>
+  <si>
+    <t>bondage (বন্ধন, দাসত্ব)</t>
+  </si>
+  <si>
+    <t>minor (অপ্রধান)</t>
+  </si>
+  <si>
+    <t>major (প্রধান)</t>
+  </si>
+  <si>
+    <t>motion (চলমানতা)</t>
+  </si>
+  <si>
+    <t>stillness (নিশ্চলতা)</t>
+  </si>
+  <si>
+    <t>masculine (পুং-জাতীয়)</t>
+  </si>
+  <si>
+    <t>feminine (স্ত্রী-জাতীয়)</t>
+  </si>
+  <si>
+    <t>old (বৃদ্ধ)</t>
+  </si>
+  <si>
+    <t>young (তরুণ)</t>
+  </si>
+  <si>
+    <t>oppose (বিরোধিতা করা)</t>
+  </si>
+  <si>
+    <t>support (সমর্থন করা)</t>
+  </si>
+  <si>
+    <t>optimism (আশাবাদ)</t>
+  </si>
+  <si>
+    <t>pessimism (নৈরাশ্যবাদ)</t>
+  </si>
+  <si>
+    <t>peevish (খিটখিটে)</t>
+  </si>
+  <si>
+    <t>genial (প্রফুল্ল)</t>
+  </si>
+  <si>
+    <t>pleasure (আনন্দ)</t>
+  </si>
+  <si>
+    <t>pain (যন্ত্রণা)</t>
+  </si>
+  <si>
+    <t>professional (পেশাদার)</t>
+  </si>
+  <si>
+    <t>amateur (অপেশাদার)</t>
+  </si>
+  <si>
+    <t>quick (দ্রুত)</t>
+  </si>
+  <si>
+    <t>slow (ধীর)</t>
+  </si>
+  <si>
+    <t>reduce (হ্রাস করা)</t>
+  </si>
+  <si>
+    <t>increase (বৃদ্ধি করা)</t>
+  </si>
+  <si>
+    <t>retreat (পশ্চাদপসরণ)</t>
+  </si>
+  <si>
+    <t>advance (অগ্রগতি)</t>
+  </si>
+  <si>
+    <t>reveal (প্রকাশ করা)</t>
+  </si>
+  <si>
+    <t>conceal (গোপন করা)</t>
+  </si>
+  <si>
+    <t>rude (রুক্ষ)</t>
+  </si>
+  <si>
+    <t>polite (নম্র)</t>
+  </si>
+  <si>
+    <t>rich (ধনী)</t>
+  </si>
+  <si>
+    <t>poor (দরিদ্র)</t>
+  </si>
+  <si>
+    <t>right (ঠিক)</t>
+  </si>
+  <si>
+    <t>wrong (ভুল)</t>
+  </si>
+  <si>
+    <t>strict (কড়া)</t>
+  </si>
+  <si>
+    <t>lenient (শিথিল)</t>
+  </si>
+  <si>
+    <t>strong (শক্তিশালী)</t>
+  </si>
+  <si>
+    <t>weak (দুর্বল)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shy (লাজুক) </t>
+  </si>
+  <si>
+    <t>shameless (নির্লজ্জ)</t>
+  </si>
+  <si>
+    <t>slumber (নিদ্রা)</t>
+  </si>
+  <si>
+    <t>wakefulness (জাগরণ)</t>
+  </si>
+  <si>
+    <t>sullen (বিষণ্ণ)</t>
+  </si>
+  <si>
+    <t>cheerful (প্রফুল্ল)</t>
+  </si>
+  <si>
+    <t>survive (বেঁচে থাকা)</t>
+  </si>
+  <si>
+    <t>die (মরা)</t>
+  </si>
+  <si>
+    <t>tall (লম্বা)</t>
+  </si>
+  <si>
+    <t>dwarf (বেঁটে)</t>
+  </si>
+  <si>
+    <t>top (শীর্ষ)</t>
+  </si>
+  <si>
+    <t>bottom (তলদেশ)</t>
+  </si>
+  <si>
+    <t>touchy (খিটখিটে)</t>
+  </si>
+  <si>
+    <t>ugly (কুশ্রী)</t>
+  </si>
+  <si>
+    <t>beautiful (সুশ্রী)</t>
+  </si>
+  <si>
+    <t>unity (ঐক্য)</t>
+  </si>
+  <si>
+    <t>diversity (বৈচিত্র্য)</t>
+  </si>
+  <si>
+    <t>vague (অস্পষ্ট)</t>
+  </si>
+  <si>
+    <t>clear (পরিষ্কার)</t>
+  </si>
+  <si>
+    <t>war (যুদ্ধ)</t>
+  </si>
+  <si>
+    <t>peace (শান্তি)</t>
+  </si>
+  <si>
+    <t>wary (সতর্ক)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> rash (গোঁয়ার, হঠকারী)</t>
+  </si>
+  <si>
+    <t>weal (সুখ)</t>
+  </si>
+  <si>
+    <t>woe (দুঃখ)</t>
+  </si>
+  <si>
+    <t>decay (শুকিয়ে যাওয়া, ক্ষয় পাওয়া)</t>
+  </si>
+  <si>
+    <t>flourish, thrive (বিকাশ লাভ করা)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="20">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3665,6 +4644,24 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -3731,11 +4728,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -3816,10 +4814,20 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="19" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="2"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -4358,6 +5366,15 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B91"/>
@@ -6092,6 +7109,1380 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C165"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="40.42578125" style="41" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="47.85546875" style="41" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.7109375" style="41" customWidth="1"/>
+    <col min="4" max="16384" width="9.140625" style="41"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" s="40" customFormat="1">
+      <c r="A1" s="40" t="s">
+        <v>917</v>
+      </c>
+      <c r="B1" s="40" t="s">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="41" t="s">
+        <v>919</v>
+      </c>
+      <c r="B2" s="41" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="41" t="s">
+        <v>921</v>
+      </c>
+      <c r="B3" s="41" t="s">
+        <v>922</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="41" t="s">
+        <v>923</v>
+      </c>
+      <c r="B4" s="41" t="s">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="41" t="s">
+        <v>925</v>
+      </c>
+      <c r="B5" s="41" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="41" t="s">
+        <v>927</v>
+      </c>
+      <c r="B6" s="41" t="s">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="41" t="s">
+        <v>929</v>
+      </c>
+      <c r="B7" s="41" t="s">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="41" t="s">
+        <v>931</v>
+      </c>
+      <c r="B8" s="41" t="s">
+        <v>932</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" s="41" t="s">
+        <v>933</v>
+      </c>
+      <c r="B9" s="41" t="s">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" s="41" t="s">
+        <v>935</v>
+      </c>
+      <c r="B10" s="41" t="s">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="41" t="s">
+        <v>937</v>
+      </c>
+      <c r="B11" s="41" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="41" t="s">
+        <v>939</v>
+      </c>
+      <c r="B12" s="41" t="s">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" s="41" t="s">
+        <v>941</v>
+      </c>
+      <c r="B13" s="41" t="s">
+        <v>942</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="41" t="s">
+        <v>943</v>
+      </c>
+      <c r="B14" s="41" t="s">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" s="41" t="s">
+        <v>945</v>
+      </c>
+      <c r="B15" s="41" t="s">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" s="41" t="s">
+        <v>947</v>
+      </c>
+      <c r="B16" s="41" t="s">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="41" t="s">
+        <v>949</v>
+      </c>
+      <c r="B17" s="41" t="s">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="41" t="s">
+        <v>951</v>
+      </c>
+      <c r="B18" s="41" t="s">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="41" t="s">
+        <v>953</v>
+      </c>
+      <c r="B19" s="41" t="s">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" s="41" t="s">
+        <v>955</v>
+      </c>
+      <c r="B20" s="41" t="s">
+        <v>956</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="41" t="s">
+        <v>957</v>
+      </c>
+      <c r="B21" s="41" t="s">
+        <v>958</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" s="41" t="s">
+        <v>959</v>
+      </c>
+      <c r="B22" s="41" t="s">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" s="41" t="s">
+        <v>961</v>
+      </c>
+      <c r="B23" s="41" t="s">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" s="41" t="s">
+        <v>963</v>
+      </c>
+      <c r="B24" s="41" t="s">
+        <v>964</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" s="41" t="s">
+        <v>965</v>
+      </c>
+      <c r="B25" s="41" t="s">
+        <v>966</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" s="41" t="s">
+        <v>967</v>
+      </c>
+      <c r="B26" s="41" t="s">
+        <v>968</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" s="41" t="s">
+        <v>969</v>
+      </c>
+      <c r="B27" s="41" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" s="41" t="s">
+        <v>971</v>
+      </c>
+      <c r="B28" s="41" t="s">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" s="41" t="s">
+        <v>973</v>
+      </c>
+      <c r="B29" s="41" t="s">
+        <v>974</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" s="41" t="s">
+        <v>975</v>
+      </c>
+      <c r="B30" s="41" t="s">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" s="41" t="s">
+        <v>977</v>
+      </c>
+      <c r="B31" s="41" t="s">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" s="41" t="s">
+        <v>979</v>
+      </c>
+      <c r="B32" s="41" t="s">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" s="41" t="s">
+        <v>981</v>
+      </c>
+      <c r="B33" s="41" t="s">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" s="41" t="s">
+        <v>983</v>
+      </c>
+      <c r="B34" s="41" t="s">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" s="41" t="s">
+        <v>985</v>
+      </c>
+      <c r="B35" s="41" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" s="41" t="s">
+        <v>987</v>
+      </c>
+      <c r="B36" s="41" t="s">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" s="41" t="s">
+        <v>989</v>
+      </c>
+      <c r="B37" s="41" t="s">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" s="41" t="s">
+        <v>991</v>
+      </c>
+      <c r="B38" s="41" t="s">
+        <v>992</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" s="41" t="s">
+        <v>993</v>
+      </c>
+      <c r="B39" s="41" t="s">
+        <v>994</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" s="41" t="s">
+        <v>995</v>
+      </c>
+      <c r="B40" s="41" t="s">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" s="41" t="s">
+        <v>997</v>
+      </c>
+      <c r="B41" s="41" t="s">
+        <v>998</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" s="41" t="s">
+        <v>999</v>
+      </c>
+      <c r="B42" s="41" t="s">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43" s="41" t="s">
+        <v>1001</v>
+      </c>
+      <c r="B43" s="41" t="s">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44" s="41" t="s">
+        <v>919</v>
+      </c>
+      <c r="B44" s="41" t="s">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45" s="41" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B45" s="41" t="s">
+        <v>1005</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46" s="41" t="s">
+        <v>1006</v>
+      </c>
+      <c r="B46" s="41" t="s">
+        <v>1007</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47" s="41" t="s">
+        <v>1008</v>
+      </c>
+      <c r="B47" s="41" t="s">
+        <v>1009</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48" s="41" t="s">
+        <v>1010</v>
+      </c>
+      <c r="B48" s="41" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49" s="41" t="s">
+        <v>1012</v>
+      </c>
+      <c r="B49" s="41" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50" s="41" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B50" s="41" t="s">
+        <v>1015</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51" s="41" t="s">
+        <v>1016</v>
+      </c>
+      <c r="B51" s="41" t="s">
+        <v>1017</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52" s="41" t="s">
+        <v>1018</v>
+      </c>
+      <c r="B52" s="41" t="s">
+        <v>1019</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53" s="41" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B53" s="41" t="s">
+        <v>1021</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54" s="41" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B54" s="41" t="s">
+        <v>1023</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55" s="41" t="s">
+        <v>1024</v>
+      </c>
+      <c r="B55" s="41" t="s">
+        <v>1025</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56" s="41" t="s">
+        <v>1026</v>
+      </c>
+      <c r="B56" s="41" t="s">
+        <v>1027</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57" s="41" t="s">
+        <v>1028</v>
+      </c>
+      <c r="B57" s="41" t="s">
+        <v>1029</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58" s="41" t="s">
+        <v>1030</v>
+      </c>
+      <c r="B58" s="41" t="s">
+        <v>1031</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59" s="41" t="s">
+        <v>1032</v>
+      </c>
+      <c r="B59" s="41" t="s">
+        <v>1033</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60" s="41" t="s">
+        <v>1034</v>
+      </c>
+      <c r="B60" s="41" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61" s="41" t="s">
+        <v>1036</v>
+      </c>
+      <c r="B61" s="41" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62" s="41" t="s">
+        <v>1038</v>
+      </c>
+      <c r="B62" s="41" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
+      <c r="A63" s="41" t="s">
+        <v>1040</v>
+      </c>
+      <c r="B63" s="41" t="s">
+        <v>1041</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
+      <c r="A64" s="41" t="s">
+        <v>1042</v>
+      </c>
+      <c r="B64" s="41" t="s">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
+      <c r="A65" s="41" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B65" s="41" t="s">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
+      <c r="A66" s="41" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B66" s="41" t="s">
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2">
+      <c r="A67" s="41" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B67" s="41" t="s">
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
+      <c r="A68" s="41" t="s">
+        <v>1050</v>
+      </c>
+      <c r="B68" s="41" t="s">
+        <v>1051</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2">
+      <c r="A69" s="41" t="s">
+        <v>1052</v>
+      </c>
+      <c r="B69" s="41" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2">
+      <c r="A70" s="41" t="s">
+        <v>1054</v>
+      </c>
+      <c r="B70" s="41" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2">
+      <c r="A71" s="41" t="s">
+        <v>1056</v>
+      </c>
+      <c r="B71" s="41" t="s">
+        <v>1057</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2">
+      <c r="A72" s="41" t="s">
+        <v>1058</v>
+      </c>
+      <c r="B72" s="41" t="s">
+        <v>1059</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
+      <c r="A73" s="41" t="s">
+        <v>1060</v>
+      </c>
+      <c r="B73" s="41" t="s">
+        <v>1061</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
+      <c r="A74" s="41" t="s">
+        <v>1062</v>
+      </c>
+      <c r="B74" s="41" t="s">
+        <v>1063</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75" s="41" t="s">
+        <v>1064</v>
+      </c>
+      <c r="B75" s="41" t="s">
+        <v>1065</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76" s="41" t="s">
+        <v>1066</v>
+      </c>
+      <c r="B76" s="41" t="s">
+        <v>1067</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77" s="41" t="s">
+        <v>1068</v>
+      </c>
+      <c r="B77" s="41" t="s">
+        <v>1069</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
+      <c r="A78" s="41" t="s">
+        <v>1070</v>
+      </c>
+      <c r="B78" s="41" t="s">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
+      <c r="A79" s="41" t="s">
+        <v>1072</v>
+      </c>
+      <c r="B79" s="41" t="s">
+        <v>1073</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
+      <c r="A80" s="41" t="s">
+        <v>1074</v>
+      </c>
+      <c r="B80" s="41" t="s">
+        <v>1075</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
+      <c r="A81" s="41" t="s">
+        <v>1076</v>
+      </c>
+      <c r="B81" s="41" t="s">
+        <v>1077</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2">
+      <c r="A82" s="41" t="s">
+        <v>1078</v>
+      </c>
+      <c r="B82" s="41" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2">
+      <c r="A83" s="41" t="s">
+        <v>1080</v>
+      </c>
+      <c r="B83" s="41" t="s">
+        <v>1081</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2">
+      <c r="A84" s="41" t="s">
+        <v>927</v>
+      </c>
+      <c r="B84" s="41" t="s">
+        <v>1082</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2">
+      <c r="A85" s="41" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B85" s="41" t="s">
+        <v>1084</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2">
+      <c r="A86" s="41" t="s">
+        <v>1085</v>
+      </c>
+      <c r="B86" s="41" t="s">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2">
+      <c r="A87" s="41" t="s">
+        <v>1087</v>
+      </c>
+      <c r="B87" s="41" t="s">
+        <v>1088</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2">
+      <c r="A88" s="41" t="s">
+        <v>1089</v>
+      </c>
+      <c r="B88" s="41" t="s">
+        <v>1090</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2">
+      <c r="A89" s="41" t="s">
+        <v>1091</v>
+      </c>
+      <c r="B89" s="41" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2">
+      <c r="A90" s="41" t="s">
+        <v>1093</v>
+      </c>
+      <c r="B90" s="41" t="s">
+        <v>1094</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2">
+      <c r="A91" s="41" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B91" s="41" t="s">
+        <v>1096</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2">
+      <c r="A92" s="41" t="s">
+        <v>1097</v>
+      </c>
+      <c r="B92" s="41" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2">
+      <c r="A93" s="41" t="s">
+        <v>1099</v>
+      </c>
+      <c r="B93" s="41" t="s">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2">
+      <c r="A94" s="41" t="s">
+        <v>1101</v>
+      </c>
+      <c r="B94" s="41" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2">
+      <c r="A95" s="41" t="s">
+        <v>1103</v>
+      </c>
+      <c r="B95" s="41" t="s">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2">
+      <c r="A96" s="41" t="s">
+        <v>1105</v>
+      </c>
+      <c r="B96" s="41" t="s">
+        <v>1106</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2">
+      <c r="A97" s="41" t="s">
+        <v>1107</v>
+      </c>
+      <c r="B97" s="41" t="s">
+        <v>1108</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2">
+      <c r="A98" s="41" t="s">
+        <v>1109</v>
+      </c>
+      <c r="B98" s="41" t="s">
+        <v>1110</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2">
+      <c r="A99" s="41" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B99" s="41" t="s">
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2">
+      <c r="A100" s="41" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B100" s="41" t="s">
+        <v>1114</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2">
+      <c r="A101" s="41" t="s">
+        <v>1115</v>
+      </c>
+      <c r="B101" s="41" t="s">
+        <v>1116</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2">
+      <c r="A102" s="41" t="s">
+        <v>939</v>
+      </c>
+      <c r="B102" s="41" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2">
+      <c r="A103" s="41" t="s">
+        <v>1118</v>
+      </c>
+      <c r="B103" s="41" t="s">
+        <v>1119</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2">
+      <c r="A104" s="41" t="s">
+        <v>1120</v>
+      </c>
+      <c r="B104" s="41" t="s">
+        <v>1121</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2">
+      <c r="A105" s="41" t="s">
+        <v>1122</v>
+      </c>
+      <c r="B105" s="41" t="s">
+        <v>1123</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2">
+      <c r="A106" s="41" t="s">
+        <v>1124</v>
+      </c>
+      <c r="B106" s="41" t="s">
+        <v>1125</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2">
+      <c r="A107" s="41" t="s">
+        <v>1126</v>
+      </c>
+      <c r="B107" s="41" t="s">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2">
+      <c r="A108" s="41" t="s">
+        <v>1128</v>
+      </c>
+      <c r="B108" s="41" t="s">
+        <v>1129</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2">
+      <c r="A109" s="41" t="s">
+        <v>1130</v>
+      </c>
+      <c r="B109" s="41" t="s">
+        <v>1131</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2">
+      <c r="A110" s="41" t="s">
+        <v>1132</v>
+      </c>
+      <c r="B110" s="41" t="s">
+        <v>1133</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2">
+      <c r="A111" s="41" t="s">
+        <v>1134</v>
+      </c>
+      <c r="B111" s="41" t="s">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2">
+      <c r="A112" s="41" t="s">
+        <v>1136</v>
+      </c>
+      <c r="B112" s="41" t="s">
+        <v>1137</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3">
+      <c r="A113" s="41" t="s">
+        <v>1138</v>
+      </c>
+      <c r="B113" s="41" t="s">
+        <v>1139</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3">
+      <c r="A114" s="41" t="s">
+        <v>1140</v>
+      </c>
+      <c r="B114" s="41" t="s">
+        <v>1141</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3">
+      <c r="A115" s="41" t="s">
+        <v>1142</v>
+      </c>
+      <c r="B115" s="41" t="s">
+        <v>1143</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3">
+      <c r="A116" s="41" t="s">
+        <v>1144</v>
+      </c>
+      <c r="B116" s="41" t="s">
+        <v>1145</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3">
+      <c r="A117" s="41" t="s">
+        <v>1146</v>
+      </c>
+      <c r="B117" s="41" t="s">
+        <v>1147</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3">
+      <c r="A118" s="41" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B118" s="41" t="s">
+        <v>1149</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3">
+      <c r="A119" s="41" t="s">
+        <v>1150</v>
+      </c>
+      <c r="B119" s="41" t="s">
+        <v>1151</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3">
+      <c r="A120" s="41" t="s">
+        <v>1152</v>
+      </c>
+      <c r="B120" s="41" t="s">
+        <v>1153</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3">
+      <c r="A121" s="41" t="s">
+        <v>1154</v>
+      </c>
+      <c r="B121" s="41" t="s">
+        <v>1155</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3">
+      <c r="A122" s="41" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B122" s="41" t="s">
+        <v>1157</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3">
+      <c r="A123" s="41" t="s">
+        <v>1158</v>
+      </c>
+      <c r="B123" s="41" t="s">
+        <v>1159</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3">
+      <c r="A124" s="42" t="s">
+        <v>1160</v>
+      </c>
+      <c r="B124" s="42" t="s">
+        <v>1161</v>
+      </c>
+      <c r="C124" s="43"/>
+    </row>
+    <row r="125" spans="1:3">
+      <c r="A125" s="42" t="s">
+        <v>1162</v>
+      </c>
+      <c r="B125" s="42" t="s">
+        <v>1163</v>
+      </c>
+      <c r="C125" s="43"/>
+    </row>
+    <row r="126" spans="1:3">
+      <c r="A126" s="42" t="s">
+        <v>1164</v>
+      </c>
+      <c r="B126" s="42" t="s">
+        <v>1165</v>
+      </c>
+      <c r="C126" s="43"/>
+    </row>
+    <row r="127" spans="1:3">
+      <c r="A127" s="42" t="s">
+        <v>1166</v>
+      </c>
+      <c r="B127" s="42" t="s">
+        <v>1167</v>
+      </c>
+      <c r="C127" s="43"/>
+    </row>
+    <row r="128" spans="1:3">
+      <c r="A128" s="42" t="s">
+        <v>1168</v>
+      </c>
+      <c r="B128" s="42" t="s">
+        <v>1169</v>
+      </c>
+      <c r="C128" s="43"/>
+    </row>
+    <row r="129" spans="1:3">
+      <c r="A129" s="42" t="s">
+        <v>1170</v>
+      </c>
+      <c r="B129" s="42" t="s">
+        <v>1171</v>
+      </c>
+      <c r="C129" s="43"/>
+    </row>
+    <row r="130" spans="1:3">
+      <c r="A130" s="42" t="s">
+        <v>1172</v>
+      </c>
+      <c r="B130" s="42" t="s">
+        <v>1173</v>
+      </c>
+      <c r="C130" s="43"/>
+    </row>
+    <row r="131" spans="1:3">
+      <c r="A131" s="42" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B131" s="42" t="s">
+        <v>1175</v>
+      </c>
+      <c r="C131" s="43"/>
+    </row>
+    <row r="132" spans="1:3">
+      <c r="A132" s="42" t="s">
+        <v>1176</v>
+      </c>
+      <c r="B132" s="42" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C132" s="43"/>
+    </row>
+    <row r="133" spans="1:3">
+      <c r="A133" s="42" t="s">
+        <v>1178</v>
+      </c>
+      <c r="B133" s="42" t="s">
+        <v>1179</v>
+      </c>
+      <c r="C133" s="42"/>
+    </row>
+    <row r="134" spans="1:3">
+      <c r="A134" s="42" t="s">
+        <v>1180</v>
+      </c>
+      <c r="B134" s="42" t="s">
+        <v>1181</v>
+      </c>
+      <c r="C134" s="43"/>
+    </row>
+    <row r="135" spans="1:3">
+      <c r="A135" s="42" t="s">
+        <v>1182</v>
+      </c>
+      <c r="B135" s="42" t="s">
+        <v>1183</v>
+      </c>
+      <c r="C135" s="43"/>
+    </row>
+    <row r="136" spans="1:3">
+      <c r="A136" s="42" t="s">
+        <v>1184</v>
+      </c>
+      <c r="B136" s="42" t="s">
+        <v>1185</v>
+      </c>
+      <c r="C136" s="43"/>
+    </row>
+    <row r="137" spans="1:3">
+      <c r="A137" s="42" t="s">
+        <v>1186</v>
+      </c>
+      <c r="B137" s="42" t="s">
+        <v>1187</v>
+      </c>
+      <c r="C137" s="43"/>
+    </row>
+    <row r="138" spans="1:3">
+      <c r="A138" s="42" t="s">
+        <v>1188</v>
+      </c>
+      <c r="B138" s="42" t="s">
+        <v>1189</v>
+      </c>
+      <c r="C138" s="43"/>
+    </row>
+    <row r="139" spans="1:3">
+      <c r="A139" s="42" t="s">
+        <v>1190</v>
+      </c>
+      <c r="B139" s="42" t="s">
+        <v>1191</v>
+      </c>
+      <c r="C139" s="43"/>
+    </row>
+    <row r="140" spans="1:3">
+      <c r="A140" s="42" t="s">
+        <v>1192</v>
+      </c>
+      <c r="B140" s="42" t="s">
+        <v>1193</v>
+      </c>
+      <c r="C140" s="43"/>
+    </row>
+    <row r="141" spans="1:3">
+      <c r="A141" s="42" t="s">
+        <v>1194</v>
+      </c>
+      <c r="B141" s="42" t="s">
+        <v>1195</v>
+      </c>
+      <c r="C141" s="43"/>
+    </row>
+    <row r="142" spans="1:3">
+      <c r="A142" s="42" t="s">
+        <v>1196</v>
+      </c>
+      <c r="B142" s="42" t="s">
+        <v>1197</v>
+      </c>
+      <c r="C142" s="43"/>
+    </row>
+    <row r="143" spans="1:3">
+      <c r="A143" s="42" t="s">
+        <v>1198</v>
+      </c>
+      <c r="B143" s="42" t="s">
+        <v>1199</v>
+      </c>
+      <c r="C143" s="43"/>
+    </row>
+    <row r="144" spans="1:3">
+      <c r="A144" s="42" t="s">
+        <v>1200</v>
+      </c>
+      <c r="B144" s="42" t="s">
+        <v>1201</v>
+      </c>
+      <c r="C144" s="43"/>
+    </row>
+    <row r="145" spans="1:3">
+      <c r="A145" s="42" t="s">
+        <v>1202</v>
+      </c>
+      <c r="B145" s="42" t="s">
+        <v>1203</v>
+      </c>
+      <c r="C145" s="43"/>
+    </row>
+    <row r="146" spans="1:3">
+      <c r="A146" s="42" t="s">
+        <v>1204</v>
+      </c>
+      <c r="B146" s="42" t="s">
+        <v>1205</v>
+      </c>
+      <c r="C146" s="43"/>
+    </row>
+    <row r="147" spans="1:3">
+      <c r="A147" s="42" t="s">
+        <v>1206</v>
+      </c>
+      <c r="B147" s="42" t="s">
+        <v>1207</v>
+      </c>
+      <c r="C147" s="43"/>
+    </row>
+    <row r="148" spans="1:3">
+      <c r="A148" s="42" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B148" s="42" t="s">
+        <v>1209</v>
+      </c>
+      <c r="C148" s="43"/>
+    </row>
+    <row r="149" spans="1:3">
+      <c r="A149" s="42" t="s">
+        <v>1210</v>
+      </c>
+      <c r="B149" s="42" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C149" s="43"/>
+    </row>
+    <row r="150" spans="1:3">
+      <c r="A150" s="42" t="s">
+        <v>1212</v>
+      </c>
+      <c r="B150" s="42" t="s">
+        <v>1213</v>
+      </c>
+      <c r="C150" s="43"/>
+    </row>
+    <row r="151" spans="1:3">
+      <c r="A151" s="42" t="s">
+        <v>1214</v>
+      </c>
+      <c r="B151" s="42" t="s">
+        <v>1215</v>
+      </c>
+      <c r="C151" s="43"/>
+    </row>
+    <row r="152" spans="1:3">
+      <c r="A152" s="42" t="s">
+        <v>1216</v>
+      </c>
+      <c r="B152" s="42" t="s">
+        <v>1217</v>
+      </c>
+      <c r="C152" s="43"/>
+    </row>
+    <row r="153" spans="1:3">
+      <c r="A153" s="42" t="s">
+        <v>1218</v>
+      </c>
+      <c r="B153" s="42" t="s">
+        <v>1219</v>
+      </c>
+      <c r="C153" s="43"/>
+    </row>
+    <row r="154" spans="1:3">
+      <c r="A154" s="42" t="s">
+        <v>1220</v>
+      </c>
+      <c r="B154" s="42" t="s">
+        <v>1221</v>
+      </c>
+      <c r="C154" s="43"/>
+    </row>
+    <row r="155" spans="1:3">
+      <c r="A155" s="42" t="s">
+        <v>1222</v>
+      </c>
+      <c r="B155" s="42" t="s">
+        <v>1223</v>
+      </c>
+      <c r="C155" s="43"/>
+    </row>
+    <row r="156" spans="1:3">
+      <c r="A156" s="42" t="s">
+        <v>1224</v>
+      </c>
+      <c r="B156" s="42" t="s">
+        <v>1225</v>
+      </c>
+      <c r="C156" s="43"/>
+    </row>
+    <row r="157" spans="1:3">
+      <c r="A157" s="42" t="s">
+        <v>1226</v>
+      </c>
+      <c r="B157" s="42" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C157" s="43"/>
+    </row>
+    <row r="158" spans="1:3">
+      <c r="A158" s="42" t="s">
+        <v>1228</v>
+      </c>
+      <c r="B158" s="42" t="s">
+        <v>1193</v>
+      </c>
+      <c r="C158" s="43"/>
+    </row>
+    <row r="159" spans="1:3">
+      <c r="A159" s="42" t="s">
+        <v>1229</v>
+      </c>
+      <c r="B159" s="42" t="s">
+        <v>1230</v>
+      </c>
+      <c r="C159" s="43"/>
+    </row>
+    <row r="160" spans="1:3">
+      <c r="A160" s="42" t="s">
+        <v>1231</v>
+      </c>
+      <c r="B160" s="42" t="s">
+        <v>1232</v>
+      </c>
+      <c r="C160" s="43"/>
+    </row>
+    <row r="161" spans="1:2">
+      <c r="A161" s="44" t="s">
+        <v>1233</v>
+      </c>
+      <c r="B161" s="44" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2">
+      <c r="A162" s="44" t="s">
+        <v>1235</v>
+      </c>
+      <c r="B162" s="44" t="s">
+        <v>1236</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2">
+      <c r="A163" s="44" t="s">
+        <v>1237</v>
+      </c>
+      <c r="B163" s="44" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2">
+      <c r="A164" s="44" t="s">
+        <v>1239</v>
+      </c>
+      <c r="B164" s="44" t="s">
+        <v>1240</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2">
+      <c r="A165" s="44" t="s">
+        <v>1241</v>
+      </c>
+      <c r="B165" s="44" t="s">
+        <v>1242</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B160"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
@@ -7214,7 +9605,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
@@ -7318,7 +9709,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B62"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -7831,7 +10222,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B62"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
@@ -8345,7 +10736,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B29"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8592,13 +10983,4 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/question_bank/ENGLISH - Vocabulary.xlsx
+++ b/question_bank/ENGLISH - Vocabulary.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7500" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7500" firstSheet="6" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="Syllabus" sheetId="29" r:id="rId1"/>
@@ -21,9 +21,8 @@
     <sheet name="One Word Subs" sheetId="17" r:id="rId7"/>
     <sheet name="One Word Subs (MS)" sheetId="16" r:id="rId8"/>
     <sheet name="One Word Subs (Guide)" sheetId="21" r:id="rId9"/>
-    <sheet name="Correct Spelling" sheetId="12" r:id="rId10"/>
   </sheets>
-  <calcPr calcId="162913" refMode="R1C1"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -33,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1341" uniqueCount="1243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1342" uniqueCount="1244">
   <si>
     <t>Amazing</t>
   </si>
@@ -4494,6 +4493,9 @@
   </si>
   <si>
     <t>flourish, thrive (বিকাশ লাভ করা)</t>
+  </si>
+  <si>
+    <t>Syllabus</t>
   </si>
 </sst>
 </file>
@@ -5225,152 +5227,229 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:A27"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="139.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:1">
+    <row r="1" spans="1:2" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>1243</v>
+      </c>
+      <c r="B1" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
         <v>886</v>
       </c>
-    </row>
-    <row r="3" spans="1:1">
+      <c r="B2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
       <c r="A3" t="s">
         <v>887</v>
       </c>
-    </row>
-    <row r="4" spans="1:1">
+      <c r="B3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
       <c r="A4" t="s">
         <v>888</v>
       </c>
-    </row>
-    <row r="5" spans="1:1">
+      <c r="B4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
       <c r="A5" t="s">
         <v>889</v>
       </c>
-    </row>
-    <row r="6" spans="1:1">
+      <c r="B5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
       <c r="A6" t="s">
         <v>890</v>
       </c>
-    </row>
-    <row r="7" spans="1:1">
+      <c r="B6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
       <c r="A7" t="s">
         <v>891</v>
       </c>
-    </row>
-    <row r="8" spans="1:1">
+      <c r="B7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
       <c r="A8" t="s">
         <v>892</v>
       </c>
-    </row>
-    <row r="9" spans="1:1">
+      <c r="B8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
       <c r="A9" t="s">
         <v>893</v>
       </c>
-    </row>
-    <row r="10" spans="1:1">
+      <c r="B9">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
       <c r="A10" t="s">
         <v>894</v>
       </c>
-    </row>
-    <row r="11" spans="1:1">
+      <c r="B10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
       <c r="A11" t="s">
         <v>895</v>
       </c>
-    </row>
-    <row r="12" spans="1:1">
+      <c r="B11">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
       <c r="A12" t="s">
         <v>896</v>
       </c>
-    </row>
-    <row r="13" spans="1:1">
+      <c r="B12">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
       <c r="A13" t="s">
         <v>897</v>
       </c>
-    </row>
-    <row r="14" spans="1:1">
+      <c r="B13">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
       <c r="A14" t="s">
         <v>898</v>
       </c>
-    </row>
-    <row r="15" spans="1:1">
+      <c r="B14">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
       <c r="A15" t="s">
         <v>899</v>
       </c>
-    </row>
-    <row r="16" spans="1:1">
+      <c r="B15">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
       <c r="A16" t="s">
         <v>900</v>
       </c>
-    </row>
-    <row r="17" spans="1:1">
+      <c r="B16">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
       <c r="A17" t="s">
         <v>901</v>
       </c>
-    </row>
-    <row r="18" spans="1:1">
+      <c r="B17">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
       <c r="A18" t="s">
         <v>902</v>
       </c>
-    </row>
-    <row r="19" spans="1:1">
+      <c r="B18">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
       <c r="A19" s="23" t="s">
         <v>903</v>
       </c>
-    </row>
-    <row r="20" spans="1:1">
+      <c r="B19">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
       <c r="A20" t="s">
         <v>904</v>
       </c>
-    </row>
-    <row r="21" spans="1:1">
+      <c r="B20">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
       <c r="A21" t="s">
         <v>905</v>
       </c>
-    </row>
-    <row r="22" spans="1:1">
+      <c r="B21">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
       <c r="A22" t="s">
         <v>906</v>
       </c>
-    </row>
-    <row r="23" spans="1:1">
+      <c r="B22">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
       <c r="A23" t="s">
         <v>907</v>
       </c>
-    </row>
-    <row r="24" spans="1:1">
+      <c r="B23">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
       <c r="A24" t="s">
         <v>908</v>
       </c>
-    </row>
-    <row r="25" spans="1:1">
+      <c r="B24">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
       <c r="A25" s="39" t="s">
         <v>909</v>
       </c>
-    </row>
-    <row r="26" spans="1:1">
+      <c r="B25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
       <c r="A26" t="s">
         <v>910</v>
       </c>
-    </row>
-    <row r="27" spans="1:1">
+      <c r="B26">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
       <c r="A27" t="s">
         <v>911</v>
       </c>
+      <c r="B27">
+        <v>27</v>
+      </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
